--- a/artfynd/A 47274-2024 artfynd.xlsx
+++ b/artfynd/A 47274-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -788,6 +788,1674 @@
           <t>Stora Obrutna Skogsområden</t>
         </is>
       </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>120617511</v>
+      </c>
+      <c r="B3" t="n">
+        <v>91858</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Rotmyren, Rotmyren, Upl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>702931</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6659343</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Häverö</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>120599053</v>
+      </c>
+      <c r="B4" t="n">
+        <v>105032</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Rotmyren, Rotmyren, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>703040</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6659246</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Häverö</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>120596538</v>
+      </c>
+      <c r="B5" t="n">
+        <v>97930</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Rotmyren, Rotmyren, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>702844</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6659257</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Häverö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>120596683</v>
+      </c>
+      <c r="B6" t="n">
+        <v>90580</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Rotmyren, Rotmyren, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>702922</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6659144</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Häverö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>120600055</v>
+      </c>
+      <c r="B7" t="n">
+        <v>97930</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Rotmyren, Rotmyren, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>703056</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6659258</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Häverö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>120608993</v>
+      </c>
+      <c r="B8" t="n">
+        <v>91881</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Rotmyren, Rotmyren, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>703480</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6659603</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Häverö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>120596867</v>
+      </c>
+      <c r="B9" t="n">
+        <v>5168</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>102204</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Grönhjon</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Callidium aeneum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(De Geer, 1775)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Långrudan, Långrudan, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>702979</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6659114</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Häverö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>120611152</v>
+      </c>
+      <c r="B10" t="n">
+        <v>97930</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Rotmyren, Rotmyren, Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>703387</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6659553</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Häverö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>120617422</v>
+      </c>
+      <c r="B11" t="n">
+        <v>91881</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Rotmyren, Rotmyren, Upl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>702948</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6659336</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Häverö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>120611443</v>
+      </c>
+      <c r="B12" t="n">
+        <v>91512</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Scop.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Rotmyren, Rotmyren, Upl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>703385</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6659523</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Häverö</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>120609377</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79160</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Rotmyren, Rotmyren, Upl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>703454</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6659624</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Häverö</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>120596781</v>
+      </c>
+      <c r="B14" t="n">
+        <v>100194</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Rotmyren, Rotmyren, Upl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>702970</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6659129</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Häverö</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>120605775</v>
+      </c>
+      <c r="B15" t="n">
+        <v>90580</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Rotmyren, Rotmyren, Upl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>703361</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6659328</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Häverö</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>120608702</v>
+      </c>
+      <c r="B16" t="n">
+        <v>91881</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Rotmyren, Rotmyren, Upl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>703444</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6659577</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Häverö</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>120613848</v>
+      </c>
+      <c r="B17" t="n">
+        <v>97930</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Rotmyren, Rotmyren, Upl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>703211</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6659581</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Häverö</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>120596988</v>
+      </c>
+      <c r="B18" t="n">
+        <v>105032</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Rotmyren, Rotmyren, Upl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>703042</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6659192</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Häverö</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 47274-2024 artfynd.xlsx
+++ b/artfynd/A 47274-2024 artfynd.xlsx
@@ -675,53 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>106521436</v>
+        <v>120596683</v>
       </c>
       <c r="B2" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Stormossen, Upl</t>
+          <t>Rotmyren, Rotmyren, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>702970.3379353908</v>
+        <v>702922</v>
       </c>
       <c r="R2" t="n">
-        <v>6659192.09155087</v>
+        <v>6659144</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-10-20</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-10-20</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,53 +760,44 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>David Falk</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>David Falk, David Falk</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Stora Obrutna Skogsområden</t>
-        </is>
-      </c>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120611443</v>
+        <v>120605775</v>
       </c>
       <c r="B3" t="n">
-        <v>91612</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4769</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>703385</v>
+        <v>703361</v>
       </c>
       <c r="R3" t="n">
-        <v>6659523</v>
+        <v>6659328</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -893,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120596867</v>
+        <v>120617511</v>
       </c>
       <c r="B4" t="n">
-        <v>5168</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -909,34 +880,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102204</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Långrudan, Långrudan, Upl</t>
+          <t>Rotmyren, Rotmyren, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>702979</v>
+        <v>702931</v>
       </c>
       <c r="R4" t="n">
-        <v>6659114</v>
+        <v>6659343</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -995,37 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120608993</v>
+        <v>120611443</v>
       </c>
       <c r="B5" t="n">
-        <v>91990</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>4769</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1035,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>703480</v>
+        <v>703385</v>
       </c>
       <c r="R5" t="n">
-        <v>6659603</v>
+        <v>6659523</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1097,59 +1063,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120596538</v>
+        <v>120608702</v>
       </c>
       <c r="B6" t="n">
-        <v>98056</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Rotmyren, Rotmyren, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>702844</v>
+        <v>703444</v>
       </c>
       <c r="R6" t="n">
-        <v>6659257</v>
+        <v>6659577</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1208,37 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120596781</v>
+        <v>120608993</v>
       </c>
       <c r="B7" t="n">
-        <v>100322</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>5966</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1248,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>702970</v>
+        <v>703480</v>
       </c>
       <c r="R7" t="n">
-        <v>6659129</v>
+        <v>6659603</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1310,59 +1257,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120613848</v>
+        <v>120617422</v>
       </c>
       <c r="B8" t="n">
-        <v>98056</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Rotmyren, Rotmyren, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>703211</v>
+        <v>702948</v>
       </c>
       <c r="R8" t="n">
-        <v>6659581</v>
+        <v>6659336</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1421,15 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120605775</v>
+        <v>120609377</v>
       </c>
       <c r="B9" t="n">
-        <v>90679</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1437,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1461,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>703361</v>
+        <v>703454</v>
       </c>
       <c r="R9" t="n">
-        <v>6659328</v>
+        <v>6659624</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,50 +1451,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120617511</v>
+        <v>120596867</v>
       </c>
       <c r="B10" t="n">
-        <v>91955</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5178</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>102204</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Rotmyren, Rotmyren, Upl</t>
+          <t>Långrudan, Långrudan, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>702931</v>
+        <v>702979</v>
       </c>
       <c r="R10" t="n">
-        <v>6659343</v>
+        <v>6659114</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1625,50 +1548,54 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120599053</v>
+        <v>120596538</v>
       </c>
       <c r="B11" t="n">
-        <v>105161</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Rotmyren, Rotmyren, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>703040</v>
+        <v>702844</v>
       </c>
       <c r="R11" t="n">
-        <v>6659246</v>
+        <v>6659257</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1727,50 +1654,54 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120609377</v>
+        <v>120600055</v>
       </c>
       <c r="B12" t="n">
-        <v>79212</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Rotmyren, Rotmyren, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>703454</v>
+        <v>703056</v>
       </c>
       <c r="R12" t="n">
-        <v>6659624</v>
+        <v>6659258</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1829,50 +1760,54 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120596683</v>
+        <v>120611152</v>
       </c>
       <c r="B13" t="n">
-        <v>90679</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Rotmyren, Rotmyren, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>702922</v>
+        <v>703387</v>
       </c>
       <c r="R13" t="n">
-        <v>6659144</v>
+        <v>6659553</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1931,50 +1866,54 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120596988</v>
+        <v>120613848</v>
       </c>
       <c r="B14" t="n">
-        <v>105161</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Rotmyren, Rotmyren, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>703042</v>
+        <v>703211</v>
       </c>
       <c r="R14" t="n">
-        <v>6659192</v>
+        <v>6659581</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2033,59 +1972,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120600055</v>
+        <v>120596988</v>
       </c>
       <c r="B15" t="n">
-        <v>98056</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Rotmyren, Rotmyren, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>703056</v>
+        <v>703042</v>
       </c>
       <c r="R15" t="n">
-        <v>6659258</v>
+        <v>6659192</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2144,37 +2069,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120617422</v>
+        <v>120599053</v>
       </c>
       <c r="B16" t="n">
-        <v>91990</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5966</v>
+        <v>221144</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2184,10 +2104,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>702948</v>
+        <v>703040</v>
       </c>
       <c r="R16" t="n">
-        <v>6659336</v>
+        <v>6659246</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2246,62 +2166,48 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120611152</v>
+        <v>106521436</v>
       </c>
       <c r="B17" t="n">
-        <v>98056</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Rotmyren, Rotmyren, Upl</t>
+          <t>Stormossen, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>703387</v>
+        <v>702971</v>
       </c>
       <c r="R17" t="n">
-        <v>6659553</v>
+        <v>6659192</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2325,12 +2231,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
+          <t>2022-10-20</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
+          <t>2022-10-20</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2345,49 +2251,48 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>David Falk</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr"/>
+          <t>David Falk, David Falk</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Stora Obrutna Skogsområden</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120608702</v>
+        <v>120596781</v>
       </c>
       <c r="B18" t="n">
-        <v>91990</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5966</v>
+        <v>222498</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2397,10 +2302,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>703444</v>
+        <v>702970</v>
       </c>
       <c r="R18" t="n">
-        <v>6659577</v>
+        <v>6659129</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 47274-2024 artfynd.xlsx
+++ b/artfynd/A 47274-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120596683</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120605775</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120617511</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120611443</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120608702</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120608993</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120617422</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120609377</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120596867</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1651,6 +1701,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120596538</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1757,6 +1812,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120600055</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1863,6 +1923,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120611152</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1969,6 +2034,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120613848</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2066,6 +2136,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120596988</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2163,6 +2238,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120599053</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2264,6 +2344,11 @@
           <t>Stora Obrutna Skogsområden</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106521436</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2361,8 +2446,32 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120596781</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>